--- a/ParkWise/chat logs.xlsx
+++ b/ParkWise/chat logs.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11122"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E424F028-AA02-EA42-9BF6-F2BBF645A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="5180" yWindow="2200" windowWidth="14800" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>https://gemini.google.com/share/98ef6d6c73e6</t>
   </si>
@@ -41,16 +42,22 @@
   <si>
     <t>Stav's</t>
   </si>
+  <si>
+    <t>https://gemini.google.com/share/7bee023d22f1</t>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/941c043cd85b</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -58,7 +65,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -89,8 +96,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="היפר-קישור" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="היפר-קישור" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -98,14 +105,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -143,7 +153,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -215,7 +225,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -388,15 +398,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47.5" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -404,62 +414,70 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1"/>
-    <hyperlink ref="A6" r:id="rId2"/>
-    <hyperlink ref="A2" r:id="rId3"/>
-    <hyperlink ref="A3" r:id="rId4"/>
-    <hyperlink ref="A4" r:id="rId5"/>
-    <hyperlink ref="A5" r:id="rId6"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B2" r:id="rId7" xr:uid="{F7979752-65E4-564E-AA23-34CF39EC2990}"/>
+    <hyperlink ref="B3" r:id="rId8" xr:uid="{F594546A-160A-B045-A001-379BC0FD263A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ParkWise/chat logs.xlsx
+++ b/ParkWise/chat logs.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11122"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E424F028-AA02-EA42-9BF6-F2BBF645A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="2200" windowWidth="14800" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="2205" windowWidth="14805" windowHeight="8025"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -17,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>https://gemini.google.com/share/98ef6d6c73e6</t>
   </si>
@@ -25,18 +24,9 @@
     <t>https://gemini.google.com/share/3ae7d9e40768</t>
   </si>
   <si>
-    <t>https://gemini.google.com/share/a9071f9e38b7</t>
-  </si>
-  <si>
     <t>https://gemini.google.com/share/2a7e3f26b336</t>
   </si>
   <si>
-    <t>https://gemini.google.com/share/7b887a377d37</t>
-  </si>
-  <si>
-    <t>https://gemini.google.com/share/98db4696d689</t>
-  </si>
-  <si>
     <t>Lana's</t>
   </si>
   <si>
@@ -52,12 +42,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -65,7 +55,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -96,8 +86,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="היפר-קישור" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -113,9 +103,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -153,7 +143,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -225,7 +215,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -398,86 +388,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.5" customWidth="1"/>
-    <col min="2" max="2" width="42.6640625" customWidth="1"/>
+    <col min="1" max="1" width="47.42578125" customWidth="1"/>
+    <col min="2" max="2" width="57.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B2" r:id="rId7" xr:uid="{F7979752-65E4-564E-AA23-34CF39EC2990}"/>
-    <hyperlink ref="B3" r:id="rId8" xr:uid="{F594546A-160A-B045-A001-379BC0FD263A}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="B2" r:id="rId4"/>
+    <hyperlink ref="B3" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
